--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260903.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260903.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>136,595</t>
+          <t>137,675</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.53%</t>
+          <t>26.53%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>98,940</t>
+          <t>99,740</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.92%</t>
+          <t>8.29%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>15,585</t>
+          <t>15,685</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.89%</t>
+          <t>7.97%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>50,365</t>
+          <t>50,765</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.71%</t>
+          <t>5.72%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>119,995</t>
+          <t>120,955</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.47%</t>
+          <t>5.49%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>59,030</t>
+          <t>59,500</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.43%</t>
+          <t>4.67%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>5,635</t>
+          <t>5,735</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>64,725</t>
+          <t>65,245</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>19,535</t>
+          <t>19,695</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>44,635</t>
+          <t>44,995</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>18,183</t>
+          <t>18,283</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>76,135</t>
+          <t>76,745</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -875,56 +875,56 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>31,170</t>
+          <t>31,430</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>117,970,418</t>
+          <t>20,245</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>20,085</t>
+          <t>109,936,178</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>50,395</t>
+          <t>50,845</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>26,238</t>
+          <t>26,478</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>19,330</t>
+          <t>19,490</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>35,760</t>
+          <t>36,050</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>58,728</t>
+          <t>59,198</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>11,581</t>
+          <t>11,681</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>21,138</t>
+          <t>21,308</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>7,890</t>
+          <t>7,990</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>18,205</t>
+          <t>18,355</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>125,285</t>
+          <t>125,985</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1161,56 +1161,56 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>15,741</t>
+          <t>15,871</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>9,536</t>
+          <t>19,587</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>19,437</t>
+          <t>9,636</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>42,590</t>
+          <t>42,930</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>37,040</t>
+          <t>37,340</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>11,645</t>
+          <t>11,745</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>607,326</t>
+          <t>375,446</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>-231,880</t>
+          <t>5,414</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
